--- a/InputData/elec/GHESS/Green Hydrogen Electricity Supply Shareweights.xlsx
+++ b/InputData/elec/GHESS/Green Hydrogen Electricity Supply Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndonesiaEPS/Shared Documents/Updated Indonesia InputData files/elec/GHESS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\elec\GHESS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11E51E6-BA89-4879-AFE0-0753A63A9214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8B2864-1A2B-40F4-A6BB-7D9E0B76D4EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32445" yWindow="4185" windowWidth="19200" windowHeight="11205" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1275,108 +1275,111 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE25"/>
+  <dimension ref="A1:AF25"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1">
+        <v>2020</v>
+      </c>
+      <c r="C1">
         <v>2021</v>
       </c>
-      <c r="C1">
+      <c r="D1">
         <v>2022</v>
       </c>
-      <c r="D1">
+      <c r="E1">
         <v>2023</v>
       </c>
-      <c r="E1">
+      <c r="F1">
         <v>2024</v>
       </c>
-      <c r="F1">
+      <c r="G1">
         <v>2025</v>
       </c>
-      <c r="G1">
+      <c r="H1">
         <v>2026</v>
       </c>
-      <c r="H1">
+      <c r="I1">
         <v>2027</v>
       </c>
-      <c r="I1">
+      <c r="J1">
         <v>2028</v>
       </c>
-      <c r="J1">
+      <c r="K1">
         <v>2029</v>
       </c>
-      <c r="K1">
+      <c r="L1">
         <v>2030</v>
       </c>
-      <c r="L1">
+      <c r="M1">
         <v>2031</v>
       </c>
-      <c r="M1">
+      <c r="N1">
         <v>2032</v>
       </c>
-      <c r="N1">
+      <c r="O1">
         <v>2033</v>
       </c>
-      <c r="O1">
+      <c r="P1">
         <v>2034</v>
       </c>
-      <c r="P1">
+      <c r="Q1">
         <v>2035</v>
       </c>
-      <c r="Q1">
+      <c r="R1">
         <v>2036</v>
       </c>
-      <c r="R1">
+      <c r="S1">
         <v>2037</v>
       </c>
-      <c r="S1">
+      <c r="T1">
         <v>2038</v>
       </c>
-      <c r="T1">
+      <c r="U1">
         <v>2039</v>
       </c>
-      <c r="U1">
+      <c r="V1">
         <v>2040</v>
       </c>
-      <c r="V1">
+      <c r="W1">
         <v>2041</v>
       </c>
-      <c r="W1">
+      <c r="X1">
         <v>2042</v>
       </c>
-      <c r="X1">
+      <c r="Y1">
         <v>2043</v>
       </c>
-      <c r="Y1">
+      <c r="Z1">
         <v>2044</v>
       </c>
-      <c r="Z1">
+      <c r="AA1">
         <v>2045</v>
       </c>
-      <c r="AA1">
+      <c r="AB1">
         <v>2046</v>
       </c>
-      <c r="AB1">
+      <c r="AC1">
         <v>2047</v>
       </c>
-      <c r="AC1">
+      <c r="AD1">
         <v>2048</v>
       </c>
-      <c r="AD1">
+      <c r="AE1">
         <v>2049</v>
       </c>
-      <c r="AE1">
+      <c r="AF1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1470,8 +1473,11 @@
       <c r="AE2">
         <v>0</v>
       </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1565,8 +1571,11 @@
       <c r="AE3">
         <v>0</v>
       </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1660,8 +1669,11 @@
       <c r="AE4">
         <v>0</v>
       </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1755,8 +1767,11 @@
       <c r="AE5">
         <v>0</v>
       </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1850,8 +1865,11 @@
       <c r="AE6">
         <v>0</v>
       </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1945,8 +1963,11 @@
       <c r="AE7">
         <v>1</v>
       </c>
+      <c r="AF7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2040,8 +2061,11 @@
       <c r="AE8">
         <v>1</v>
       </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2135,8 +2159,11 @@
       <c r="AE9">
         <v>0</v>
       </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2230,8 +2257,11 @@
       <c r="AE10">
         <v>0</v>
       </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2325,8 +2355,11 @@
       <c r="AE11">
         <v>0</v>
       </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2420,8 +2453,11 @@
       <c r="AE12">
         <v>0</v>
       </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2515,8 +2551,11 @@
       <c r="AE13">
         <v>0</v>
       </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2610,8 +2649,11 @@
       <c r="AE14">
         <v>0</v>
       </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2705,8 +2747,11 @@
       <c r="AE15">
         <v>0</v>
       </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2800,8 +2845,11 @@
       <c r="AE16">
         <v>0</v>
       </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2895,8 +2943,11 @@
       <c r="AE17">
         <v>0</v>
       </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2990,8 +3041,11 @@
       <c r="AE18">
         <v>0</v>
       </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -3085,8 +3139,11 @@
       <c r="AE19">
         <v>0</v>
       </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -3180,8 +3237,11 @@
       <c r="AE20">
         <v>0</v>
       </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3275,8 +3335,11 @@
       <c r="AE21">
         <v>0</v>
       </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -3370,8 +3433,11 @@
       <c r="AE22">
         <v>0</v>
       </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -3465,8 +3531,11 @@
       <c r="AE23">
         <v>0</v>
       </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>23</v>
       </c>
@@ -3560,8 +3629,11 @@
       <c r="AE24">
         <v>0</v>
       </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>24</v>
       </c>
@@ -3653,6 +3725,9 @@
         <v>0</v>
       </c>
       <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
         <v>0</v>
       </c>
     </row>
@@ -3662,6 +3737,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
     <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
@@ -3805,22 +3895,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CDD9067-D90C-4ED2-BD96-67C1BD579897}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A135B7C-68BF-4D31-A66E-7370AA5E3E86}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0648F8B-880E-4806-A18D-F004C0764CAB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3836,21 +3928,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A135B7C-68BF-4D31-A66E-7370AA5E3E86}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CDD9067-D90C-4ED2-BD96-67C1BD579897}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>